--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0188.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0188.xlsx
@@ -27551,7 +27551,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Nguy hiểm quá. Để ta lo.</t>
+          <t>Nguy hiểm quá. Để tao lo.</t>
         </is>
       </c>
     </row>
@@ -27811,7 +27811,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Haha. Ngày xưa có một tay lái xe bí ẩn thường qua lại vùng này, thỉnh thoảng ta lại gặp hắn khi bảo trì mạch điện.</t>
+          <t>Haha. Ngày xưa có một tay lái xe bí ẩn thường qua lại vùng này, thỉnh thoảng tao lại gặp hắn khi bảo trì mạch điện.</t>
         </is>
       </c>
     </row>
@@ -29111,7 +29111,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Nếu không có {Male=anh ấy;Female=cô ấy}, tôi đã chẳng thể đạt được thành tựu như ngày hôm nay!</t>
+          <t>Nếu không có {Male=him;Female=her}, tôi đã chẳng thể đạt được thành tựu như ngày hôm nay!</t>
         </is>
       </c>
     </row>
@@ -29696,7 +29696,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Cái gì đây?</t>
+          <t>Cái gì vậy?</t>
         </is>
       </c>
     </row>
@@ -29891,7 +29891,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Ta nhanh hơn trước nhiều, cậu không thấy à? Haha.</t>
+          <t>Tao nhanh hơn trước nhiều, cậu không thấy à? Haha.</t>
         </is>
       </c>
     </row>
@@ -30021,7 +30021,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao rồi?</t>
         </is>
       </c>
     </row>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Muốn ta giả làm khách hàng của cậu lần nữa không?</t>
+          <t>Muốn tao giả làm khách hàng của cậu lần nữa không?</t>
         </is>
       </c>
     </row>
@@ -30801,7 +30801,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -30866,7 +30866,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Haha, không có gì nghiêm trọng đâu. Ta chỉ lo cho nó thôi. Ta biết nó có thể làm được gì, mà thành công đến nhanh thế này...</t>
+          <t>Haha, không có gì nghiêm trọng đâu. Tao chỉ lo cho nó thôi. Tao biết nó có thể làm được gì, mà thành công đến nhanh thế này...</t>
         </is>
       </c>
     </row>
@@ -31126,7 +31126,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Ui da… lại tô vẽ hoài công. Này! {Male=Thưa ngài;Female=Thưa cô} có muốn một bức chân dung không?</t>
+          <t>Ui da… lại tô vẽ hoài công. Này! {Male=Sir;Female=Miss} có muốn một bức chân dung không?</t>
         </is>
       </c>
     </row>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Ui da... Gọi ta là Rover là được rồi.</t>
+          <t>Ui da... Gọi tao là Rover là được rồi.</t>
         </is>
       </c>
     </row>
@@ -32621,7 +32621,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
